--- a/publications/data.xlsx
+++ b/publications/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91720c579d88d817/Documents/GitHub/rjjanse.github.io/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56461E0B-7BF8-48EA-92B9-EF63A5396957}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56DEE162-1E3D-42CF-8E77-113101B1E2D1}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="4575" windowWidth="11760" windowHeight="19920" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>id</t>
   </si>
@@ -276,6 +276,234 @@
   </si>
   <si>
     <t>CKD-MBD biomarkers and symptom burden</t>
+  </si>
+  <si>
+    <t>Acute kidney injury and kidney replacement therapy in COVID-19: a systematic review and meta-analysis</t>
+  </si>
+  <si>
+    <t>Fu EL, Janse RJ, de Jong Y, van der Endt VHW, Milders J, van der Willik EM, de Rooij ENM, Dekkers EM, Rotmans JI, van Diepen M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: Acute kidney injury (AKI) can affect hospitalized patients with coronavirus disease 2019 (COVID-19), with estimates ranging between 0.5% and 40%. We performed a systematic review and meta-analysis of studies reporting incidence, mortality and risk factors for AKI in hospitalized COVID-19 patients. Methods: We systematically searched 11 electronic databases until 29 May 2020 for studies in English reporting original data on AKI and kidney replacement therapy (KRT) in hospitalized COVID-19 patients. Incidences of AKI and KRT and risk ratios for mortality associated with AKI were pooled using generalized linear mixed and random-effects models. Potential risk factors for AKI were assessed using meta-regression. Incidences were stratified by geographic location and disease severity. Results: A total of 3042 articles were identified, of which 142 studies were included, with 49 048 hospitalized COVID-19 patients including 5152 AKI events. The risk of bias of included studies was generally low. The pooled incidence of AKI was 28.6% [95% confidence interval (CI) 19.8-39.5] among hospitalized COVID-19 patients from the USA and Europe (20 studies) and 5.5% (95% CI 4.1-7.4) among patients from China (62 studies), whereas the pooled incidence of KRT was 7.7% (95% CI 5.1-11.4; 18 studies) and 2.2% (95% CI 1.5-3.3; 52 studies), respectively. Among patients admitted to the intensive care unit, the incidence of KRT was 20.6% (95% CI 15.7-26.7; 38 studies). Meta-regression analyses showed that age, male sex, cardiovascular disease, diabetes mellitus, hypertension and chronic kidney disease were associated with the occurrence of AKI; in itself, AKI was associated with an increased risk of mortality, with a pooled risk ratio of 4.6 (95% CI 3.3-6.5). Discussion: AKI and KRT are common events in hospitalized COVID-19 patients, with estimates varying across geographic locations. Additional studies are needed to better understand the underlying mechanisms and optimal treatment of AKI in these patients. </t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 02 September 2020</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfaa160</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/32897278/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/32897278</t>
+  </si>
+  <si>
+    <t>Janse RJ, Hoekstra T, Jager KJ, Zoccali C, Tripepi G, Dekker FW, van Diepen M</t>
+  </si>
+  <si>
+    <t>Conducting correlation analysis: important limitations and pitfalls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The correlation coefficient is a statistical measure often used in studies to show an association between variables or to look at the agreement between two methods. In this paper, we will discuss not only the basics of the correlation coefficient, such as its assumptions and how it is interpreted, but also important limitations when using the correlation coefficient, such as its assumption of a linear association and its sensitivity to the range of observations. We will also discuss why the coefficient is invalid when used to assess agreement of two methods aiming to measure a certain value, and discuss better alternatives, such as the intraclass coefficient and Bland-Altman's limits of agreement. The concepts discussed in this paper are supported with examples from literature in the field of nephrology. </t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 03 May 2021</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfab085</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/34754428/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/34754428</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/janse-2021-ckj</t>
+  </si>
+  <si>
+    <t>Comparative effectiveness of SGLT2i versus GLP1-RA on cardiovascular outcomes in routine clinical practice</t>
+  </si>
+  <si>
+    <t>Fu EL, Clase CM,Janse RJ, Lindholm B, Dekker FW, Jardine MJ, Carrero JJ</t>
+  </si>
+  <si>
+    <t>Background: To investigate the comparative effectiveness of sodium-glucose cotransporter 2 inhibitors (SGLT2i) and glucagon-like peptide 1 receptor agonists (GLP1-RA) on cardiovascular outcomes in routine clinical practice, which have never been directly compared in head-to-head outcome trials. Methods: We compared outcomes of adults who newly started SGLT2i or GLP1-RA therapy in Stockholm, Sweden, during 2013-2019. The primary outcome was major adverse cardiovascular events (MACE), a composite of cardiovascular (CV) death, myocardial infarction and stroke. Secondary outcomes included the individual MACE components and hospitalization for heart failure. Cox regression with propensity score overlap weighting was used to estimate hazard ratios (HRs) with 95% confidence intervals and adjust for 57 covariates. Results: We included 12,375 individuals, of which 5489 initiated SGLT2i and 6886 GLP1-RA therapy, followed for median 1.6 years. Mean age was 61 years and 37.6% were women. Compared with GLP1-RA, SGLT2i new users had similar risk of MACE risk (adjusted HR 1.04; 95% CI 0.83-1.31). The adjusted HRs (95% CI) for SGLT2i vs. GLP1-RA were 0.80 (0.59-1.09) for heart failure hospitalization, 0.95 (0.58-1.55) for cardiovascular death, 0.91 (0.67-1.24) for myocardial infarction and 1.71 (1.14-2.59) for ischemic stroke (5-year absolute risk difference for stroke 1.9% [95% CI 0.8-3.0]). Discussion: In a largely primary-prevention population of people undergoing routine care, no differences were observed in MACE risk among initiators of SGLT2i and GLP1-RA. However, compared with GLP1RA, the use of SGLT2i was associated with an increased risk of ischemic stroke that was small in absolute magnitude.</t>
+  </si>
+  <si>
+    <t>International Journal of Cardiology - 21 January 2022</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ijcard.2022.01.042</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/35074492/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/35074492</t>
+  </si>
+  <si>
+    <t>Stopping versus continuing renin-angiotensin-system inhibitors after acute kidney injury and adverse clinical outcomes: an observational study from routine care data</t>
+  </si>
+  <si>
+    <t>Janse RJ, Fu EL, Clase CM, Tomlinson L, Lindholm B, van Diepen M, Dekker FW, Carrero JJ</t>
+  </si>
+  <si>
+    <t>Background: The risk-benefit ratio of continuing with renin-angiotensin system inhibitors (RASi) after an episode of acute kidney injury (AKI) is unclear. While stopping RASi may prevent recurrent AKI or hyperkalaemia, it may deprive patients of the cardiovascular benefits of using RASi. Methods: We analysed outcomes of long-term RASi users experiencing AKI (stage 2 or 3, or clinically coded) during hospitalization in Stockholm and Sweden during 2007-18. We compared stopping RASi within 3 months after discharge with continuing RASi. The primary study outcome was the composite of all-cause mortality, myocardial infarction (MI) and stroke. Recurrent AKI was our secondary outcome and we considered hyperkalaemia as a positive control outcome. Propensity score overlap weighted Cox models were used to estimate hazard ratios (HRs), balancing 75 confounders. Weighted absolute risk differences (ARDs) were also determined. Results: We included 10 165 individuals, of whom 4429 stopped and 5736 continued RASi, with a median follow-up of 2.3 years. The median age was 78 years; 45% were women and median kidney function before the index episode of AKI was 55 mL/min/1.73 m2. After weighting, those who stopped had an increased risk [HR, 95% confidence interval (CI)] of the composite of death, MI and stroke [1.13, 1.07-1.19; ARD 3.7, 95% CI 2.6-4.8] compared with those who continued, a similar risk of recurrent AKI (0.94, 0.84-1.05) and a decreased risk of hyperkalaemia (0.79, 0.71-0.88). Discussion: Stopping RASi use among survivors of moderate-to-severe AKI was associated with a similar risk of recurrent AKI, but higher risk of the composite of death, MI and stroke.</t>
+  </si>
+  <si>
+    <t>Use of guideline-recommended medical therapy in patients with heart failure and chronic kidney disease: from physician's prescriptions to patient's dispensations, medication adherence and persistence</t>
+  </si>
+  <si>
+    <t>Janse RJ, Fu EL, Dahlström U, Benson L, Lindholm B, van Diepen M, Dekker FW, Lund LH, Carrero JJ, Savarese G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aim: Half of heart failure (HF) patients have chronic kidney disease (CKD) complicating their pharmacological management. We evaluated physicians' and patients' patterns of use of evidence-based medical therapies in HF across CKD stages. Methods and results: We studied HF patients with reduced (HFrEF) and mildly reduced (HFmrEF) ejection fraction enrolled in the Swedish Heart Failure Registry in 2009-2018. We investigated the likelihood of physicians to prescribe guideline-recommended therapies to patients with CKD, and of patients to fill the prescriptions within 90 days of incident HF (initiating therapy), to adhere (proportion of days covered ≥80%) and persist (continued use) on these treatments during the first year of therapy. We identified 31 668 patients with HFrEF (median age 74 years, 46% CKD). The proportions receiving a prescription for angiotensin-converting enzyme inhibitors/angiotensin receptor blockers/angiotensin receptor-neprilysin inhibitors (ACEi/ARB/ARNi) were 96%, 92%, 86%, and 68%, for estimated glomerular filtration rate (eGFR) ≥60, 45-59, 30-44, and &lt;30 ml/min/1.73m2 , respectively; for beta-blockers 94%, 93%, 92%, and 92%, for mineralocorticoid receptor antagonists (MRAs) 45%, 44%, 37%, 24%; and for triple therapy (combination of ACEi/ARB/ARNi + beta-blockers + MRA) 38%, 35%, 28%, and 15%. Patients with CKD were less likely to initiate these medications, and less likely to adhere to and persist on ACEi/ARB/ARNi, MRA, and triple therapy. Among stoppers, CKD patients were less likely to restart these medications. Results were consistent after multivariable adjustment and in patients with HFmrEF (n = 15 114). Conclusions: Patients with HF and CKD are less likely to be prescribed and to fill prescriptions for evidence-based therapies, showing lower adherence and persistence, even at eGFR categories where these therapies are recommended and have shown efficacy in clinical trials. </t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 12 January 2022</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfac003</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/35664269/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/35664269</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/janse-2022-ckj</t>
+  </si>
+  <si>
+    <t>European Journal of Heart Failure - 18 July 2022</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/ejhf.2620</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/35851740/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/35851740</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/janse-2022-ejhf</t>
+  </si>
+  <si>
+    <t>Response to: 'Twelve tips for introducing very short answer questions (VSAQs) into your medical curriculum'</t>
+  </si>
+  <si>
+    <t>van Wijk EV, Janse RJ, Langers AMJ</t>
+  </si>
+  <si>
+    <t>Very-short-answer-questions (VSAQs) are an alternative to the shortcomings of multiple choice questions in medical education. Recently, Bala, et al. published twelve tips to implement VSAQs into the medical curriculum and we further supplement these with our own experience.</t>
+  </si>
+  <si>
+    <t>Medical Teacher - 19 December 2022</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/0142159X.2022.2158070</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/36534759/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/36534759</t>
+  </si>
+  <si>
+    <t>Prevalence of chronic kidney disease in women of reproductive age and observed birth rates</t>
+  </si>
+  <si>
+    <t>Vrijlandt WAL, de Jong MFC, Prins JR, Bramham K, Vrijlandt PJWS, Janse RJ, Mazhar F, Carrero JJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction: Women of reproductive age with chronic kidney disease (CKD) are recognised to have decreased fertility and a higher risk of adverse pregnancy outcomes. How often CKD afflicts women of reproductive age is not well known. This study aimed to evaluate the burden of CKD and associated birth rates in an entire region. Methods: This was a retrospective cohort study including women of childbearing age in Stockholm during 2006-2015. We estimated the prevalence of 'probable CKD' by the presence of an ICD-10 diagnosis of CKD, a single estimated glomerular filtration rate (eGFR) &lt;60 mL/min/1.73 m2 or history of maintenance dialysis. By linkage with the Swedish Medical Birth Register we identified births during the subsequent three years from study inclusion and evaluated birth rates. Results: We identified 817,730 women in our region, of whom 55% had at least one creatinine measurement. A total of 3938 women were identified as having probable CKD, providing an age-averaged CKD prevalence of 0.50%. Women with probable CKD showed a lower birth rate 3 years after the index date (35.7 children per 1000 person years) than the remaining women free from CKD (46.5 children per 1000 person years). Conclusion:  As many as 0.50% of individuals in this cohort had probable CKD, defined on the basis of at least one eGFR &lt;60 ml/min/1.73m2 test result, dialysis treatment (i.e. CKD stages 3-5) or an ICD-10 diagnosis of CKD. This prevalence is lower than previous estimates. Women with probable CKD, according to a study mainly capturing CKD 3-5, had a lower birth rate than those without CKD, illustrating the challenges of this population to successfully conceive. </t>
+  </si>
+  <si>
+    <t>Journal of Nephrology - 18 January 2023</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s40620-022-01546-z</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/36652169/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/36652169</t>
+  </si>
+  <si>
+    <t>Systematic meta-review of prediction studies demonstrates stable trends in bias and low PROBAST inter-rater agreement</t>
+  </si>
+  <si>
+    <t>Langenhuijsen LFS, Janse RJ, Venema E, Kent DM, van Diepen M, Dekker FW, Steyerberg EW, de Jong Y</t>
+  </si>
+  <si>
+    <t>Objectives: To 1) explore trends of risk of bias (ROB) in prediction research over time following key methodological publications, using the Prediction model Risk Of Bias ASsessment Tool (PROBAST) and 2) assess the inter-rater agreement of the PROBAST. Study design and setting: PubMed and Web of Science were searched for reviews with extractable PROBAST scores on domain and signaling question (SQ) level. ROB trends were visually correlated with yearly citations of key-publications. Inter-rater agreement was assessed using Cohen’s Kappa. Results: 139 systematic reviews were included, of which 85 reviews (containing 2477 single studies) on domain level and 54 reviews (containing 2458 single studies) on SQ level. High ROB was prevalent, especially in the Analysis domain, and overall trends of ROB remained relatively stable over time. The inter-rater agreement was low, both on domain (Kappa 0.04-0.26) and SQ level (Kappa -0.14-0.49). Conclusion: Prediction model studies are at high ROB and time trends in ROB as assessed with the PROBAST remain relatively stable. These results might be explained by key-publications having no influence on ROB or recency of key-publications. Moreover, the trend may suffer from the low inter-rater agreement and ceiling effect of the PROBAST. The inter-rater agreement could potentially be improved by altering the PROBAST or providing training on how to apply the PROBAST.</t>
+  </si>
+  <si>
+    <t>Journal of Clinical Epidemiology - 02 May 2023</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jclinepi.2023.04.012</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/37142166/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/37142166</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/langenhuijsen-2023-jce</t>
+  </si>
+  <si>
+    <t>Albuminuria and the risk of cancer: the Stockholm Creatinine Measurements (SCREAM) project</t>
+  </si>
+  <si>
+    <t>Luo L, Yang Y, Kieneker LM, Janse RJ, Bosi A, Mazhar F, de Boer RA, de Bock GH, Gansevoort RT, Carrero JJ</t>
+  </si>
+  <si>
+    <t>Background: Studies investigating the association of chronic kidney disease and cancer have focused on estimated glomerular filtration (eGFR) rather than on albuminuria. This study aimed to examine whether albuminuria is associated with cancer incidence, and whether this association is independent of eGFR. Methods: We included subjects of the Stockholm Creatinine Measurements (SCREAM) project without a history of cancer, 250 768 subjects with at least 1 urine albumin-creatinine ratio (ACR) test (primary cohort), and 433 850 subjects with at least 1 dipstick albuminuria test (secondary cohort). Albuminuria was quantified as KDIGO albuminuria stages. The primary outcome was overall cancer incidence. Secondary outcomes were site-specific cancer incidence rates. Multivariable Cox proportional hazards regression models adjusted for confounders including eGFR to calculate hazard ratios (HRs, 95% CIs). Results: During a median follow-up of 4.3 (IQR, 2.0–8.2) years, 21 901 subjects of the ACR cohort developed de novo cancer. In multivariable analyses, adjusting among others for eGFR, subjects with an ACR of 30-299 mg/g or ≥300 mg/g had a 23% (HR, 1.23; 95% CI, 1.19–1.28) and 40% (HR, 1.40; 95% CI, 1.31–1.50) higher risk of developing cancer, respectively, when compared to subjects with an ACR &lt;30 mg/g. This graded, independent association was also observed for urinary tract, gastrointestinal tract, lung, and hematological cancer incidence (all P &lt; 0.05). Results were similar in the dipstick albuminuria cohort. Conclusions: Albuminuria was associated with the risk of cancer independent of eGFR. This association was primarily driven by a higher risk of urinary tract, gastrointestinal tract, lung, and hematological cancers.</t>
+  </si>
+  <si>
+    <t>Use of very short answer questions compared to multiple choice questions in undergraduate medical students: an external validation study</t>
+  </si>
+  <si>
+    <t>van Wijk EV, Janse RJ, Ruijter BN, Rohling JHT, van der Kraan J, Crobach S, de Jonge M, de Beaufort AJ, Dekker FW, Langers AMJ</t>
+  </si>
+  <si>
+    <t>Background: Multiple choice questions (MCQs) offer high reliability and easy machine-marking, but allow for cueing and stimulate recognition-based learning. Very short answer questions (VSAQs), which are open-ended questions requiring a very short answer, may circumvent these limitations. Although VSAQ use in medical assessment increases, almost all research on reliability and validity of VSAQs in medical education has been performed by a single research group with extensive experience in the development of VSAQs. Therefore, we aimed to validate previous findings about VSAQ reliability, discrimination, and acceptability in undergraduate medical students and teachers with limited experience in VSAQs development. Methods: To validate the results presented in previous studies, we partially replicated a previous study and extended results on student experiences. Dutch undergraduate medical students (n = 375) were randomized to VSAQs first and MCQs second or vice versa in a formative exam in two courses, to determine reliability, discrimination, and cueing. Acceptability for teachers (i.e., VSAQ review time) was determined in the summative exam. Results: Reliability (Cronbach's α) was 0.74 for VSAQs and 0.57 for MCQs in one course. In the other course, Cronbach's α was 0.87 for VSAQs and 0.83 for MCQs. Discrimination (average Rir) was 0.27 vs. 0.17 and 0.43 vs. 0.39 for VSAQs vs. MCQs, respectively. Reviewing time of one VSAQ for the entire student cohort was ±2 minutes on average. Positive cueing occurred more in MCQs than in VSAQs (20% vs. 4% and 20.8% vs. 8.3% of questions per person in both courses). Conclusions: This study validates the positive results regarding VSAQs reliability, discrimination, and acceptability in undergraduate medical students. Furthermore, we demonstrate that VSAQ use is reliable among teachers with limited experience in writing and marking VSAQs. The short learning curve for teachers, favourable marking time and applicability regardless of the topic suggest that VSAQs might also be valuable beyond medical assessment.</t>
+  </si>
+  <si>
+    <t>PLoS One - 14 July 2023</t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 23 June 2023</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfad145</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38046028/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38046028</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1371/journal.pone.0288558</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/37450485/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/37450485</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/van_wijk-2023-plos_one</t>
+  </si>
+  <si>
+    <t>last_author</t>
   </si>
 </sst>
 </file>
@@ -320,9 +548,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -658,17 +889,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C16EB68-4490-458C-8DAB-883C12CD690B}">
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -679,58 +911,61 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -740,35 +975,59 @@
       <c r="C2" t="b">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -778,23 +1037,23 @@
       <c r="C3" t="b">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -805,8 +1064,35 @@
       <c r="L3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -816,26 +1102,26 @@
       <c r="C4" t="b">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -843,8 +1129,32 @@
       <c r="L4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>98</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -854,35 +1164,62 @@
       <c r="C5" t="b">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P5" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>108</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -892,14 +1229,14 @@
       <c r="C6" t="b">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -908,19 +1245,46 @@
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O6" t="s">
+        <v>106</v>
+      </c>
+      <c r="P6" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>113</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -930,20 +1294,20 @@
       <c r="C7" t="b">
         <v>0</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -955,10 +1319,34 @@
         <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O7" t="s">
+        <v>119</v>
+      </c>
+      <c r="P7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -968,11 +1356,14 @@
       <c r="C8" t="b">
         <v>0</v>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -984,16 +1375,40 @@
         <v>0</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>125</v>
+      </c>
+      <c r="O8" t="s">
+        <v>126</v>
+      </c>
+      <c r="P8" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>128</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1003,23 +1418,23 @@
       <c r="C9" t="b">
         <v>0</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1030,8 +1445,35 @@
       <c r="L9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>132</v>
+      </c>
+      <c r="O9" t="s">
+        <v>133</v>
+      </c>
+      <c r="P9" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>135</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -1041,32 +1483,59 @@
       <c r="C10" t="b">
         <v>0</v>
       </c>
-      <c r="E10" t="b">
-        <v>0</v>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s">
+        <v>141</v>
+      </c>
+      <c r="P10" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>147</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -1076,20 +1545,20 @@
       <c r="C11" t="b">
         <v>0</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -1101,10 +1570,37 @@
         <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O11" t="s">
+        <v>144</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1114,56 +1610,59 @@
       <c r="C12" t="b">
         <v>1</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
         <v>22</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>23</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>24</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>25</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -1173,17 +1672,17 @@
       <c r="C13" t="b">
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>3</v>
       </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -1192,16 +1691,19 @@
         <v>0</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1211,32 +1713,35 @@
       <c r="C14" t="b">
         <v>0</v>
       </c>
-      <c r="E14" t="b">
+      <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1246,20 +1751,20 @@
       <c r="C15" t="b">
         <v>0</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>2</v>
       </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -1271,10 +1776,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -1284,17 +1792,17 @@
       <c r="C16" t="b">
         <v>0</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>2</v>
       </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -1303,16 +1811,19 @@
         <v>0</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1322,17 +1833,17 @@
       <c r="C17" t="b">
         <v>0</v>
       </c>
-      <c r="E17" t="b">
+      <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -1344,10 +1855,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -1357,17 +1871,17 @@
       <c r="C18" t="b">
         <v>0</v>
       </c>
-      <c r="E18" t="b">
+      <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -1379,10 +1893,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1392,14 +1909,14 @@
       <c r="C19" t="b">
         <v>1</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="b">
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -1414,13 +1931,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -1430,14 +1950,14 @@
       <c r="C20" t="b">
         <v>1</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="b">
-        <v>0</v>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -1446,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -1457,8 +1977,11 @@
       <c r="L20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -1468,32 +1991,35 @@
       <c r="C21" t="b">
         <v>0</v>
       </c>
-      <c r="E21" t="b">
+      <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -1503,17 +2029,17 @@
       <c r="C22" t="b">
         <v>1</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -1522,16 +2048,19 @@
         <v>0</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -1541,35 +2070,38 @@
       <c r="C23" t="b">
         <v>0</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>2</v>
       </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -1579,17 +2111,17 @@
       <c r="C24" t="b">
         <v>0</v>
       </c>
-      <c r="E24" t="b">
+      <c r="D24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -1601,10 +2133,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -1614,23 +2149,23 @@
       <c r="C25" t="b">
         <v>1</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -1641,8 +2176,11 @@
       <c r="L25" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -1652,32 +2190,35 @@
       <c r="C26" t="b">
         <v>0</v>
       </c>
-      <c r="E26" t="b">
+      <c r="D26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -1687,17 +2228,17 @@
       <c r="C27" t="b">
         <v>1</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -1706,25 +2247,63 @@
         <v>0</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q12" r:id="rId1" xr:uid="{EBC0A9CB-AF7B-4907-86C5-F5AEE7D86C99}"/>
-    <hyperlink ref="R12" r:id="rId2" xr:uid="{C41F3AD7-9FB3-49BE-823B-A0D373793E0D}"/>
-    <hyperlink ref="S12" r:id="rId3" xr:uid="{BCE21974-340F-45A0-B676-9490C3E63FC6}"/>
+    <hyperlink ref="R12" r:id="rId1" xr:uid="{EBC0A9CB-AF7B-4907-86C5-F5AEE7D86C99}"/>
+    <hyperlink ref="S12" r:id="rId2" xr:uid="{C41F3AD7-9FB3-49BE-823B-A0D373793E0D}"/>
+    <hyperlink ref="T12" r:id="rId3" xr:uid="{BCE21974-340F-45A0-B676-9490C3E63FC6}"/>
+    <hyperlink ref="R2" r:id="rId4" xr:uid="{B1C547D2-7C31-450D-8A24-217F4F64F23C}"/>
+    <hyperlink ref="T2" r:id="rId5" xr:uid="{0FBA6406-B72A-42E1-A12A-B4917620260E}"/>
+    <hyperlink ref="S2" r:id="rId6" xr:uid="{3D850777-FF8F-42D3-A48D-71E18AE6B10C}"/>
+    <hyperlink ref="R3" r:id="rId7" xr:uid="{6F8C8076-2DB8-47D4-ADF4-46BB20BA95BE}"/>
+    <hyperlink ref="S3" r:id="rId8" xr:uid="{34B9FEA7-33B7-451C-87AB-B209C907BC32}"/>
+    <hyperlink ref="T3" r:id="rId9" xr:uid="{157B8E88-9510-466E-9B51-401E5CA29371}"/>
+    <hyperlink ref="U3" r:id="rId10" xr:uid="{3A2D2A5B-FEDE-43BF-A63F-C5BD502A0B2C}"/>
+    <hyperlink ref="R4" r:id="rId11" xr:uid="{5BB4BDB8-B31F-4BA2-99CE-FF0A1E244A82}"/>
+    <hyperlink ref="S4" r:id="rId12" xr:uid="{A84EA7BB-5B25-4C9A-A64B-E2ADDB90AA2F}"/>
+    <hyperlink ref="U4" r:id="rId13" xr:uid="{99DD846D-A35C-4453-A7AC-A9C59C3B9429}"/>
+    <hyperlink ref="R5" r:id="rId14" xr:uid="{5A548CF2-AF45-4CEC-A721-FA47E635B777}"/>
+    <hyperlink ref="S5" r:id="rId15" xr:uid="{820428CB-BAD6-4736-B6E5-AE0A15F998D5}"/>
+    <hyperlink ref="T5" r:id="rId16" xr:uid="{8ABBC501-3598-4079-916B-57AE1A01B315}"/>
+    <hyperlink ref="U5" r:id="rId17" xr:uid="{8849A43A-CC57-469D-8779-09A90D219E49}"/>
+    <hyperlink ref="R6" r:id="rId18" xr:uid="{1E3F5A7C-598C-4B15-B7CD-9C023E102B63}"/>
+    <hyperlink ref="S6" r:id="rId19" xr:uid="{505E4B7B-7951-43E2-8F16-991DAD776839}"/>
+    <hyperlink ref="T6" r:id="rId20" xr:uid="{46ECC9B1-5D2E-4E42-9E87-33BB90226EA0}"/>
+    <hyperlink ref="U6" r:id="rId21" xr:uid="{2FBDA27D-620D-441D-AAD4-FF494F9525E8}"/>
+    <hyperlink ref="R7" r:id="rId22" xr:uid="{60640404-562B-4A78-9834-2B2905AE31D4}"/>
+    <hyperlink ref="S7" r:id="rId23" xr:uid="{F4BB8578-C031-4126-B887-575B616ACBDB}"/>
+    <hyperlink ref="T7" r:id="rId24" xr:uid="{C410AD5D-0A27-4A55-8359-B8BCCAC80675}"/>
+    <hyperlink ref="R8" r:id="rId25" xr:uid="{1AAB869A-FC56-47BB-9E6C-F20EF448F454}"/>
+    <hyperlink ref="S8" r:id="rId26" xr:uid="{1AB49950-30F9-4DB4-8DB8-819C78EBC130}"/>
+    <hyperlink ref="T8" r:id="rId27" xr:uid="{F9D2F98E-F052-4731-B8C1-844120C7E6A6}"/>
+    <hyperlink ref="R9" r:id="rId28" xr:uid="{006D434C-EA40-40C3-86F6-A19B955FE79E}"/>
+    <hyperlink ref="S9" r:id="rId29" xr:uid="{2D9902EA-1DC1-4FEC-9F96-A1FF665BA925}"/>
+    <hyperlink ref="T9" r:id="rId30" xr:uid="{46079247-A427-4CFD-A1C4-94CCB79E81D5}"/>
+    <hyperlink ref="U9" r:id="rId31" xr:uid="{1C9A3415-46CB-4E4D-AE64-70F5DB178E88}"/>
+    <hyperlink ref="R10" r:id="rId32" xr:uid="{BCF7999C-54C5-4733-AA85-670768DEF9CF}"/>
+    <hyperlink ref="S10" r:id="rId33" xr:uid="{0FD34BFC-0727-421F-AAD4-8EB505EE1F09}"/>
+    <hyperlink ref="T10" r:id="rId34" xr:uid="{8F2B826D-1177-44FE-AE85-D2173D755066}"/>
+    <hyperlink ref="R11" r:id="rId35" xr:uid="{FFD3362D-41E7-4290-8413-F577FDEC93F1}"/>
+    <hyperlink ref="S11" r:id="rId36" xr:uid="{D0273DE0-FDF7-4259-9359-895A6D75FF9B}"/>
+    <hyperlink ref="T11" r:id="rId37" xr:uid="{631C9A88-45CD-4435-AFED-B262AA65C65F}"/>
+    <hyperlink ref="U11" r:id="rId38" xr:uid="{9E72F33D-6C32-4DBE-AD0D-32AB72C38748}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/publications/data.xlsx
+++ b/publications/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91720c579d88d817/Documents/GitHub/rjjanse.github.io/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56DEE162-1E3D-42CF-8E77-113101B1E2D1}"/>
+  <xr:revisionPtr revIDLastSave="329" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F2ECCDA-1BA4-432F-BE4D-3CB2B0E689C4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
   <si>
     <t>id</t>
   </si>
@@ -504,6 +504,357 @@
   </si>
   <si>
     <t>last_author</t>
+  </si>
+  <si>
+    <t>Predicting Hospitalization and Related Outcomes in Advanced Chronic Kidney Disease: A Systematic Review, External Validation, and Development Study</t>
+  </si>
+  <si>
+    <t>Rationale &amp; objective: Hospitalization is common in patients with advanced chronic kidney disease (CKD). Predicting hospitalization and related outcomes would be beneficial for hospitals and patients. Therefore, we aimed to (1) give an overview of current prediction models for hospitalization, length of stay, and readmission in patients with advanced CKD; (2) externally validate these models; and (3) develop a new model if no valid models were identified. Study design: Systematic review, development, and external validation study. Setting &amp; participants: We were interested in prediction models of hospitalization, length of stay, or readmission for patients with advanced CKD. Our available development and validation data consisted of hemodialysis, peritoneal dialysis, and advanced CKD patients not receiving dialysis from a Dutch dialysis and European advanced CKD cohort. Selection criteria for studies:&lt;/b&gt; We systematically searched PubMed. Studies had to intentionally develop, validate, or update a prediction model in adults with CKD. Analytical approach: We used the PROBAST for risk of bias assessment. Identified models were externally validated on model discrimination (C-statistic) and calibration (calibration plot, slope, and calibration-in-the-large). We developed a Fine-Gray model for hospitalization within 1 year in patients initiating hemodialysis, accounting for the competing risk of death. Results: We identified 45 models in 8 studies. The majority were of low quality with a high risk of bias. Due to underreporting and population-specific predictors, we could only validate 3 models. These were poorly calibrated and had poor discrimination. Using multiple modelling strategies, an adequate new model could not be developed. Limitations: The outcome hospitalization might be too heterogeneous, and we did not have all relevant predictors available. Conclusions: Hospitalizations are important but difficult to predict for patients with advanced CKD. An improved prediction model should be developed, for example, using a more specific outcome (eg, cardiovascular hospitalizations) and more predictors (eg, patient-reported outcome measures).</t>
+  </si>
+  <si>
+    <t>Kidney Medicine - 25 April 2025</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.xkme.2025.101016</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40613012/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/40613012</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/janse-2025-kme</t>
+  </si>
+  <si>
+    <t>Cardiometabolic protein expression levels and pathways associated with kidney function decline in older European adults with advanced kidney disease</t>
+  </si>
+  <si>
+    <t>Aylward RE, hayward S, Chesnaye NC, Janse RJ, Jonsson PA, Torino C, Demetrio A, Szymczak M, Drechsler C, Dekker FW, Evans M, Jager KJ, Wanner C, Rayner B, Ben-Shlomo Y, Tiffin N, Caskey FJ, Birnie K</t>
+  </si>
+  <si>
+    <t>Background: Cardiovascular disease and chronic kidney disease (CKD) progression pathophysiology are similar. We investigated associations of cardiometabolic protein expression and pathways with kidney function decline in older adults with advanced CKD referred for nephrology assessment. Methods: Two plasma proteomic panels analysed at baseline (Olink® cardiometabolic T96 and cardiovascular II T96, Uppsala, Sweden) and longitudinal estimated glomerular filtration rate (eGFR) data from European adults aged &gt;65 years with a single eGFR of &lt; 20 mL/min/1.73m2 [European Quality (EQUAL) Study] were used to explore mechanisms of CKD progression. Protein-slope associations were estimated using generalized linear mixed-effects models and with a false-discovery rate P &lt; .05 taken to validation to verify the effect size of the association. Proteins were further modularized into biological pathways using pathway enrichment analysis. Results:A discovery sub-cohort of 238 complete-case participants from Germany, the UK and Poland (median age 76 years, 41% female sex, median baseline eGFR 17.8 mL/min/1.73m2) were included and 246 participants from Sweden formed the validation sub-cohort (median age 75 years, 28% female, median baseline eGFR 17.5 mL/min/1.73 m2). Of the 175 analysed proteins, higher expression levels of Receptor-type tyrosine-protein phosphatase S [-15.4% change in eGFR per year per doubling of protein expression; 95% confidence interval (CI) -23.5%, -7.6%], Insulin-like growth factor binding protein 6 (-7.9%; 95% CI -12.3%, -3.5%) and Ficolin 2 (-7.4%; 95% CI -12.0%, -2.8%) showed a validated association with eGFR decline. Conclusions: Higher expression levels of proteins and biological pathways involving fibrogenesis and the complement cascade were found to be associated with kidney function loss. However, study limitations and unavailability of concurrent kidney cellular proteomic signatures necessitate further study.</t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 18 March 2025</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfaf079</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40342947/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/40342947</t>
+  </si>
+  <si>
+    <t>When the whole is greater than the sum of its parts: why machine learning and conventional statistics are complementary for predicting future health outcomes</t>
+  </si>
+  <si>
+    <t>Janse RJ, Abu-Hanna A, Vagliano I, Stel VS, Jager KJ, Tripepi G, Zoccali C, Dekker FW, van Diepen M</t>
+  </si>
+  <si>
+    <t>An artificial intelligence boom is currently ongoing, mainly due to large language models, leading to significant interest in artificial intelligence and subsequently also in machine learning (ML). One area where ML is often applied, prediction modelling, has also long been a focus of conventional statistics. As a result, multiple studies have aimed to prove superiority of one of the two scientific disciplines over the other. However, we argue that ML and conventional statistics should not be competing fields. Instead, both fields are intertwined and complementary to each other. To illustrate this, we discuss some essentials of prediction modelling, elaborate on prediction modelling using techniques from conventional statistics, and explain prediction modelling using common ML techniques such as support vector machines, random forests, and artificial neural networks. We then showcase that conventional statistics and ML are in fact similar in many aspects, including underlying statistical concepts and methods used in model development and validation. Finally, we argue that conventional statistics and ML can and should be seen as a single integrated field. This integration can further improve prediction modelling for both disciplines (e.g. regarding fairness and reporting standards) and will support the ultimate goal: developing the best performing prediction models for the patient and healthcare provider.</t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 20 February 2025</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfaf059</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40276681/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/40276681</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/janse-2025-ckj</t>
+  </si>
+  <si>
+    <t>The battle of question formats: a comparative study of retrieval practice using very short answer questions and multiple choice questions</t>
+  </si>
+  <si>
+    <t>van Wijk EV, de Jonge M, van Blankenstein FM, Janse RJ, Langers AMJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: Retrieval practice is a highly effective learning strategy that enhances long-term retention by encouraging the active recall of information. However, the optimal question format for maximizing knowledge retention remains uncertain. In this study, we compared the effect of very short answer (VSAQ) versus multiple-choice question (MCQ) practice tests on students' knowledge retention. By analyzing these two formats, we aim to identify the most effective approach to retrieval practice, thereby helping to optimize its implementation and improve learning outcomes. Methods: In this randomized within-subjects study, students (n = 45) practiced with both VSAQs and MCQs in an extracurricular lifestyle course, without receiving feedback. The final retention test consisted of identical questions in both formats. A 2 × 2 repeated measures ANOVA was used to determine the effect of question format in practice testing and final test on final test score. Additionally, digital questionnaires were used to explore students' test-taking experiences. Results: The VSAQs were answered incorrectly more frequently on the practice tests and final test. There was no main effect of practice question format on final test performance, and no interaction effect between question format on the practice and final test. Regardless of question format, most students thought the practice tests were beneficial for learning. Conclusions: We found no evidence indicating that either MCQ or VSAQ is more effective for knowledge retention during retrieval practice. The lower initial retrieval success in the VSAQs, indicated by the higher degree of incorrect answers on the practice tests, might have limited their effectiveness during retrieval practice. To optimize the use of VSAQs in retrieval practice, it seems important to improve initial retrieval success to maximize learning outcomes. </t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s12909-024-06538-0</t>
+  </si>
+  <si>
+    <t>BMC Medical Education - 30 December 2024</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39734216/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/39734216</t>
+  </si>
+  <si>
+    <t>Informal caregiver burden in dialysis care and how it relates to patients' health-related quality of life and symptoms</t>
+  </si>
+  <si>
+    <t>Driehuis E, Janse RJ, Roeterdink AJ, Konijn WS, van Lieshout TS, Volgers TJFM, Goto NA, Broese van Groenou MI, Dekker FW, van Jaarsveld BC, Abrahams AC</t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 7 October 2024</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39493262/</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfae300</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/39493262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: Informal caregivers play a crucial role in dialysis care but may experience significant burden, potentially affecting both caregiver and patient outcomes. Research on caregiver burden and health-related quality of life (HRQoL) and the relation to patient-reported outcomes (PROs) is lacking. Therefore, we aimed to (i) describe informal caregivers' experienced burden and HRQoL and (ii) investigate how these are related to dialysis patients' HRQoL and symptoms. Methods: We conducted a cross-sectional study at dialysis initiation with 202 adult informal caregiver-dialysis patient dyads. Caregiver burden was measured with the Self-Perceived Pressure from Informal Care (SPPIC) questionnaire, HRQoL with the 12-item Short Form Health Survey (SF-12), and symptom number and burden with the Dialysis Symptom Index (DSI). Data were analysed using linear and logistic ordinal regression. Results: Around 38% of caregivers experienced moderate to high burden. Patients' lower mental HRQoL [adjusted odds ratio (aOR) = 0.95, 95% confidence interval (CI) 0.92; 0.99], higher symptom number (aOR = 1.07, 95% CI 1.02; 1.12) and higher symptom burden (aOR = 1.03, 95% CI 1.01; 1.04) were associated with greater odds of higher caregiver burden. Patients' lower mental HRQoL (β = 0.30, 95% CI 0.15; 0.46), higher symptom number (β = -0.55, 95% CI -0.78; -0.31) and higher symptom burden (β = -0.17, 95% CI -0.25; -0.10) were also associated with a lower mental HRQoL in caregivers. Conclusion: We show that a third of caregivers feel moderate to high burden and that caregiver burden is associated with patients' mental HRQoL and symptoms. These findings highlight the importance of recognizing informal caregivers and the nature of their burden. </t>
+  </si>
+  <si>
+    <t>Improving health-related quality of life after kidney transplantation using lifestyle interventions</t>
+  </si>
+  <si>
+    <t>Janse RJ, Meuleman Y</t>
+  </si>
+  <si>
+    <t>We discuss the results of the recent ACT-trial on lifestyle interventions after kidney transplantation to improve health-related quality of life, as well as how we can use these results to continue research on this topic.</t>
+  </si>
+  <si>
+    <t>The Lancet Healthy Longevity - 10 September 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.lanhl.2024.07.010</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39270689/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/39270689</t>
+  </si>
+  <si>
+    <t>Association between Chronic Kidney Disease-Mineral and Bone Disorder Biomarkers and Symptom Burden in Older Patients with Advanced Chronic Kidney Disease: Results from the EQUAL Study</t>
+  </si>
+  <si>
+    <t>Magagnoli L, Cozzolino M, Evans M, Caskey FJ, Dekker FW, Torino C, Szymczak M, Drechsler C, Pippias M, Vilasi A, Janse RJ, Krajewska M, Stel VS, Jager KJ, Chesnaye NC, the EQUAL study investigators</t>
+  </si>
+  <si>
+    <t>Clinical Journal of the American Society of Nephrology - 22 July 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2215/cjn.0000000000000510</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39037951/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/39037951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: Patients with advanced CKD develop numerous symptoms, with a multifactorial origin. Evidence linking mineral disorders (CKD-Mineral and Bone Disorder) and uremic symptoms is scant and mostly limited to dialysis patients. Here, we aim to assess the association between CKD-Mineral and Bone Disorder and symptom burden in nondialysis patients with CKD. Methods: We used data from the European Quality study, which includes patients aged ≥65 years with eGFR ≤20 ml/min per 1.73 m2 from six European countries, followed up to 5 years. We used generalized linear mixed-effect models to determine the association between repeated measurements of parathyroid hormone (PTH), phosphate, and calcium with the overall symptom number (0–33), the overall symptom severity (0–165), and the presence of 33 CKD-related symptoms. We also analyzed subgroups by sex, age, and diabetes mellitus and assessed effect mediation and joint effects between mineral biomarkers. Results: The 1396 patients included in the study had a mean of 13±6 symptoms at baseline, with a median overall severity score of 32 (interquartile range, 19–50). The association between PTH levels and symptom burden appeared U-shaped with a lower symptom burden found for mild-to-moderately increased PTH levels. Phosphate and calcium were not independently associated with overall symptom burden. The highest symptom burden was found in patients with a combination of both severe hyperparathyroidism and severe hyperphosphatemia (+2.44 symptoms [0.50–4.38], P = 0.01). The association of both hypocalcemia and hyperphosphatemia with symptom burden seemed to differ by sex and age. Conclusions: In older patients with advanced CKD not on dialysis, mild-to-moderately increased PTH was associated with a lower symptom burden, although the effect size was relatively small (less than one symptom). Neither phosphate nor calcium were associated with the overall symptom burden, except for the combination of severe hyperphosphatemia and severe hyperparathyroidism which was associated with an increased number of symptoms. </t>
+  </si>
+  <si>
+    <t>When impact trials are not feasible: alternatives to study the impact of prediction models on clinical practice</t>
+  </si>
+  <si>
+    <t>Janse RJ, Stel VS, Jager KJ, Tripepi G, Zoccali C, Dekker FW, van Diepen M</t>
+  </si>
+  <si>
+    <t>Nephrology Dialysis Transplantation - 17 July 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ndt/gfae170</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39020254/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/39020254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients with kidney disease have an uncertain future, with prognosis varying greatly per patient. To get a better idea of what the future holds and tailor interventions to the individual patient, prediction models can be of great value. Before a prediction model can be applied in practice, its performance should be measured in target populations of interest (i.e. external validation) and whether or not it helps improve clinical practice (i.e. whether it impacts clinical practice) should be determined. The impact would ideally be determined using an impact trial, but such a trial is often not feasible, and the impact of prediction models is therefore rarely assessed. As a result, prediction models that may not be so impactful may end up in clinical practice and impactful models may not be implemented due to a lack of impact studies. Ultimately, many prediction models end up never being implemented, resulting in much research waste. To allow researchers to get an indication of a prediction model's impact on clinical practice, alternative methods to assess a prediction model's impact are important. In this paper, we discuss several alternatives, including interviews, case-based surveys, decision comparisons, outcome modelling, before-after analyses and decision curve analyses. We discuss the general idea behind these approaches, including what information can be gathered from such studies and important pitfalls. Lastly, we provide examples of the different alternatives. </t>
+  </si>
+  <si>
+    <t>Adherence and persistence to novel glucose-lowering medications in persons with type 2 diabetes mellitus undergoing routine care</t>
+  </si>
+  <si>
+    <t>Janse RJ, O'Hara DV, Fu EL, Jardine MJ, Carrero JJ</t>
+  </si>
+  <si>
+    <t>Diabetes Research and Clinical Practice - 22 June 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.diabres.2024.111745</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38876274/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38876274</t>
+  </si>
+  <si>
+    <t>https://github.com/rjjanse/ohara_2024_drcp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aims: To assess adherence and persistence to sodium-glucose cotransporter-2 inhibitors (SGLT2i), glucagon-like peptide-1 receptor agonists (GLP1-RA), and dipeptidyl peptidase-4 inhibitors (DPP4i) in routine care. Methods: Using retrospective healthcare data from the Stockholm region, Sweden, we evaluated new-users of these agents during 2015-2020. We investigated adherence (≥80 % of days covered by an active supply), persistence (no treatment gap ≥ 60 days), and predictors for non-adherence and non-persistence. Results: We identified 24,470 new-users of SGLT2i (10,743), GLP1-RA (10,315), and/or DPP4i (9,488). Over 2.8 years median follow-up, the proportion demonstrating adherence was higher for SGLT2i (57 %) than DPP4i (53 %, comparison p &lt; 0.001), and for GLP1-RA than DPP4i (54 % vs 53 %, p &lt; 0.001). Similarly, persistence was higher for both SGLT2i and GLP-RA than DPP4i (respectively, 50 % vs 44 %, p &lt; 0.001; 49 % vs 44 %, p &lt; 0.001). Overall adherence was better among users who were older, had a history of high blood pressure, used more non-diabetic medications, had lower Hba1c, had better kidney function, and had completed secondary schooling or university. Women had worse adherence to SGLT2i and GLP1-RA than DPP4i. Conclusions: We report adherence and persistence to SGLT2i, GLP1-RA and DPP4i in routine care, and identify prognostic factors that could inform implementation interventions to improve uptake of these important therapies. </t>
+  </si>
+  <si>
+    <t>Does 'summative' count? The influence of the awarding of study credits on feedback use and test-taking motivation in medical progress testing</t>
+  </si>
+  <si>
+    <t>van Wijk EV, van Blankenstein FM, Donkers J, Janse RJ, Bustraan J, Adelmeijer LGM, Dubois EA, Dekker FW, Langers AMJ</t>
+  </si>
+  <si>
+    <t>Advances in Health Sciences Education: Theory and Practice - 19 March 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10459-024-10324-4</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38502460/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38502460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Despite the increasing implementation of formative assessment in medical education, its' effect on learning behaviour remains questionable. This effect may depend on how students value formative, and summative assessments differently. Informed by Expectancy Value Theory, we compared test preparation, feedback use, and test-taking motivation of medical students who either took a purely formative progress test (formative PT-group) or a progress test that yielded study credits (summative PT-group). In a mixed-methods study design, we triangulated quantitative questionnaire data (n = 264), logging data of an online PT feedback system (n = 618), and qualitative interview data (n = 21) to compare feedback use, and test-taking motivation between the formative PT-group (n = 316), and the summative PT-group (n = 302). Self-reported, and actual feedback consultation was higher in the summative PT-group. Test preparation, and active feedback use were relatively low and similar in both groups. Both quantitative, and qualitative results showed that the motivation to prepare and consult feedback relates to how students value the assessment. In the interview data, a link could be made with goal orientation theory, as performance-oriented students perceived the formative PT as not important due to the lack of study credits. This led to low test-taking effort, and feedback consultation after the formative PT. In contrast, learning-oriented students valued the formative PT, and used it for self-study or self-assessment to gain feedback. Our results indicate that most students are less motivated to put effort in the test, and use feedback when there are no direct consequences. A supportive assessment environment that emphasizes recognition of the value of formative testing is required to motivate students to use feedback for learning. </t>
+  </si>
+  <si>
+    <t>Understanding students' feedback use in medical progress testing: A qualitative interview study</t>
+  </si>
+  <si>
+    <t>van Wijk EV, van Blankenstein FM, Janse RJ, Dubois EA, Langers AMJ</t>
+  </si>
+  <si>
+    <t>Medical Education - 10 March 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/medu.15378</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38462812/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38462812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: Active engagement with feedback is crucial for feedback to be effective and improve students' learning and achievement. Medical students are provided feedback on their development in the progress test (PT), which has been implemented in various medical curricula, although its format, integration and feedback differ across institutions. Existing research on engagement with feedback in the context of PT is not sufficient to make a definitive judgement on what works and which barriers exist. Therefore, we conducted an interview study to explore students' feedback use in medical progress testing. Methods: All Dutch medical students participate in a national, curriculum-independent PT four times a year. This mandatory test, composed of multiple-choice questions, provides students with written feedback on their scores. Furthermore, an answer key is available to review their answers. Semi-structured interviews were conducted with 21 preclinical and clinical medical students who participated in the PT. Template analysis was performed on the qualitative data using a priori themes based on previous research on feedback use. Results: Template analysis revealed that students faced challenges in crucial internal psychological processes that impact feedback use, including 'awareness', 'cognizance', 'agency' and 'volition'. Factors such as stakes, available time, feedback timing and feedback presentation contributed to these difficulties, ultimately hindering feedback use. Notably, feedback engagement was higher during clinical rotations, and students were interested in the feedback when seeking insights into their performance level and career perspectives. Conclusion: Our study enhanced the understanding of students' feedback utilisation in medical progress testing by identifying key processes and factors that impact feedback use. By recognising and addressing barriers in feedback use, we can improve both student and teacher feedback literacy, thereby transforming the PT into a more valuable learning tool. </t>
+  </si>
+  <si>
+    <t>A tool to predict the risk of lower extremity amputation in patients starting dialysis</t>
+  </si>
+  <si>
+    <t>Akerboom B, Janse RJ, Caldinelli A, Lindholm B, Rotmans JI, Evans M, van Diepen M</t>
+  </si>
+  <si>
+    <t>Nephrology Dialysis Transplantation - 26 February 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ndt/gfae050</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38409858/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38409858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: Non-traumatic lower extremity amputation (LEA) is a severe complication during dialysis. To inform decision-making for physicians, we developed a multivariable prediction model for LEA after starting dialysis. Methods: Data from the Swedish Renal Registry (SNR) between 2010 and 2020 were geographically split into a development and validation cohort. Data from Netherlands Cooperative Study on the Adequacy of Dialysis (NECOSAD) between 1997 and 2009 were used for validation targeted at Dutch patients. Inclusion criteria were no previous LEA and kidney transplant and age ≥40 years at baseline. A Fine-Gray model was developed with LEA within 3 years after starting dialysis as the outcome of interest. Death and kidney transplant were treated as competing events. One coefficient, ordered by expected relevance, per 20 events was estimated. Performance was assessed with calibration and discrimination. Results: SNR was split into an urban development cohort with 4771 individuals experiencing 201 (4.8%) events and a rural validation cohort with 4.876 individuals experiencing 155 (3.2%) events. NECOSAD contained 1658 individuals experiencing 61 (3.7%) events. Ten predictors were included: female sex, age, diabetes mellitus, peripheral artery disease, cardiovascular disease, congestive heart failure, obesity, albumin, haemoglobin and diabetic retinopathy. In SNR, calibration intercept and slope were -0.003 and 0.912, respectively. The C-index was estimated as 0.813 (0.783-0.843). In NECOSAD, calibration intercept and slope were 0.001 and 1.142 respectively. The C-index was estimated as 0.760 (0.697-0.824). Calibration plots showed good calibration. Conclusion: A newly developed model to predict LEA after starting dialysis showed good discriminatory performance and calibration. By identifying high-risk individuals this model could help select patients for preventive measures. </t>
+  </si>
+  <si>
+    <t>Learning from assessment: how quality questions can stimulate learning</t>
+  </si>
+  <si>
+    <t>van Wijk E, Janse RJ, Langers AMJ</t>
+  </si>
+  <si>
+    <t>Nederlands Tijdschrift voor Geneeskunde - 01 February 2024</t>
+  </si>
+  <si>
+    <t>https://www.ntvg.nl/D8012</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38319315/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assessment plays a significant role in the career of medical doctors. Not only are they being assessed, many medical doctors are also involved in teaching which includes the creation of tests. Therefore, knowledge on high quality assessment questions is essential. Multiple-choice questions (MCQs) are commonly used, but allow for cueing, stimulates recognition-based learning and do not align clinical practice. The Very Short Answer Question (VSAQ), an open-ended question with a limited answer, is a good alternative which does not allow for cueing, is authentic and encourages students to study more actively. The marking time of VSAQs is relatively short and plausible alternative answer options are no longer needed. It's time to challenge the limits of our comfort zone and to dare using VSAQs in our assessments more often. This way, good and representative assessments can stimulate the learning process of medical doctors and form a strong fundament for professional practice. </t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38319315</t>
+  </si>
+  <si>
+    <t>An increase in albuminuria is associated with a higher incidence of malignancies</t>
+  </si>
+  <si>
+    <t>Luo L, Kieneker LM, Yang Y, Janse RJ, Bosi A, de Boer RA, Vart P, Carrero JJ, Gansevoort R</t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 12 January 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfae009</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38455523/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38455523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: A single albuminuria measurement is reported to be an independent predictor of cancer risk. Whether change in albuminuria is also independently associated with cancer is not known. Methods: We included 64 303 subjects of the Stockholm CREAtinine Measurements (SCREAM) project without a history of cancer and with at least two urine albumin-creatinine ratio (ACR) tests up to 2 years apart. Albuminuria changes were quantified by the fold-change in ACR over 2 years, and stratified into the absence of clinically elevated albuminuria (i.e. never), albuminuria that remained constant, and albuminuria that increased or decreased. The primary outcome was overall cancer incidence. Secondary outcomes were site-specific cancer incidences. Results: During a median follow-up of 3.7 (interquartile range 3.6-3.7) years, 5126 subjects developed de novo cancer. After multivariable adjustment including baseline estimated glomerular filtration rate and baseline ACR, subjects with increasing ACR over 2 years had a 19% (hazard ratio 1.19; 95% confidence interval 1.08-1.31) higher risk of overall cancer compared with those who never had clinically elevated ACR. No association with cancer risk was seen in the groups with decreasing or constant ACR. Regarding site-specific cancer risks, subjects with increasing ACR or constant ACR had a higher risk of developing urinary tract and lung cancer. No other associations between 2-year ACR changes and site-specific cancers were found. Conclusions: Increases in albuminuria over a 2-year period are associated with a higher risk of developing overall, urinary tract and lung cancer, independent of baseline kidney function and albuminuria. These data add important weight to the link that exists between albuminuria and cancer incidence. </t>
+  </si>
+  <si>
+    <t>Prognostic models in nephrology: where do we stand and where do we go from here? Mapping out the evidence in a scoping review</t>
+  </si>
+  <si>
+    <t>Milders J, Ramspek CL,  Janse RJ, Bos WJW, Rotmans JI, Dekker FW, van Diepen M</t>
+  </si>
+  <si>
+    <t>Journal of the American Society of Nephrology - 12 December 2023</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1681/asn.0000000000000285</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38082484/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/38082484</t>
+  </si>
+  <si>
+    <t>https://github.com/jmilders/milders-2023-jasn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prognostic models can strongly support individualized care provision and well-informed shared decision making. There has been an upsurge of prognostic research in the field of nephrology, but the uptake of prognostic models in clinical practice remains limited. Therefore, we map out the research field of prognostic models for kidney patients and provide directions on how to proceed from here. We performed a scoping review of studies developing, validating, or updating a prognostic model for patients with CKD. We searched all published models in PubMed and Embase and report predicted outcomes, methodological quality, and validation and/or updating efforts. We found 602 studies, of which 30.1% concerned CKD populations, 31.6% dialysis populations, and 38.4% kidney transplantation populations. The most frequently predicted outcomes were mortality ( n =129), kidney disease progression ( n =75), and kidney graft survival ( n =54). Most studies provided discrimination measures (80.4%), but much less showed calibration results (43.4%). Of the 415 development studies, 28.0% did not perform any validation and 57.6% performed only internal validation. Moreover, only 111 models (26.7%) were externally validated either in the development study itself or in an independent external validation study. Finally, in 45.8% of development studies no useable version of the model was reported. To conclude, many prognostic models have been developed for patients with CKD, mainly for outcomes related to kidney disease progression and patient/graft survival. To bridge the gap between prediction research and kidney patient care, patient-reported outcomes, methodological rigor, complete reporting of prognostic models, external validation, updating, and impact assessment urgently need more attention. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A predictor finding study found patient-reported outcomes improve the prediction of mortality of incident dialysis patients </t>
+  </si>
+  <si>
+    <t>Improving mortality prediction with PROMs</t>
+  </si>
+  <si>
+    <t>Janse RJ, Milders J, Rotmans JI, Caskey FJ, Evans M, Torino C, Szymczak M, Drechsler C, Wanner C, Pippias M, Vilasi A, Stel VS, Chesnaye NC, Jager KJ, Dekker FW, van Diepen M, the EQUAL study investigators</t>
+  </si>
+  <si>
+    <t>Milders J, Janse RJ, Bos WJW, Caskey FJ, Torino C, Vilasi A, Szymczak M, Drechsler C, Wanner C, Pippias M, Jager KJ, Chesnaye NC, Evans M, Dekker FW, van Diepen M, the EQUAL study investigators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction: Prognostic models for mortality in patients receiving dialysis primarily use clinical predictors like age, comorbidities and laboratory markers. Studies in other fields suggest that patient-reported outcomes (PROs), like pain and fatigue, can be predictors of survival. Therefore, we aimed to assess the added value of PROs to predict mortality in incident dialysis patients. Methods: Data from NECOSAD (1956 individuals) were used, and analyses were replicated in the EQUAL (415 individuals) and NECOSAD 65+ (862 individuals) studies. A base model for two-year mortality containing clinical predictors was extended using PROs (mental component score, physical component score, general health perception, depressive symptoms, number of symptoms, symptom burden, fatigue and pain). Logistic regression was used, and the added predictive performance of the PROs was evaluated using the area under the curve (AUC), measures of calibration, Brier score, likelihood ratio tests, reclassification tables, net reclassification indices, integrated discrimination improvements, and decision curve analyses. We also examined different combinations of predictors, and each PRO individually. Results: Within two years, mortality rates were 22.9%, 24.3%, and 37.1% in NECOSAD, EQUAL, and NECOSAD 65+, respectively. The base model yielded optimism-corrected AUCs of 0.806, 0.781 and 0.699, which improved to 0.826, 0.878 and 0.746 after adding the PROs. Improvement of the calibration, Brier scores, and comparative measures confirmed their predictive value. The mental and physical component score, and symptom burden had the most consistent strong performance across all cohorts. Conclusions: PROs improved prognostic models for mortality of patients receiving incident dialysis, even when added to an already well-performing model of clinical predictors. </t>
+  </si>
+  <si>
+    <t>Kidney International - 21 January 2026</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.kint.2025.07.033</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41577248/</t>
+  </si>
+  <si>
+    <t>https://europepmc.org/article/MED/41577248</t>
   </si>
 </sst>
 </file>
@@ -548,10 +899,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -570,6 +920,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1011,13 +1365,13 @@
       <c r="O2" t="s">
         <v>81</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -1150,7 +1504,7 @@
       <c r="S4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1575,25 +1929,25 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" t="s">
         <v>143</v>
       </c>
       <c r="O11" t="s">
         <v>144</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P11" t="s">
         <v>145</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="Q11" t="s">
         <v>146</v>
       </c>
-      <c r="R11" s="3" t="s">
+      <c r="R11" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="S11" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="T11" s="4" t="s">
+      <c r="T11" s="3" t="s">
         <v>153</v>
       </c>
       <c r="U11" s="1" t="s">
@@ -1702,6 +2056,30 @@
       <c r="M13" t="b">
         <v>0</v>
       </c>
+      <c r="N13" t="s">
+        <v>256</v>
+      </c>
+      <c r="O13" t="s">
+        <v>257</v>
+      </c>
+      <c r="P13" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>258</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -1716,6 +2094,9 @@
       <c r="D14" t="b">
         <v>0</v>
       </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
@@ -1739,6 +2120,27 @@
       </c>
       <c r="M14" t="b">
         <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>249</v>
+      </c>
+      <c r="O14" t="s">
+        <v>250</v>
+      </c>
+      <c r="P14" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>251</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
@@ -1781,6 +2183,27 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="s">
+        <v>242</v>
+      </c>
+      <c r="O15" t="s">
+        <v>243</v>
+      </c>
+      <c r="P15" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>244</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -1822,8 +2245,29 @@
       <c r="M16" t="b">
         <v>0</v>
       </c>
+      <c r="N16" t="s">
+        <v>235</v>
+      </c>
+      <c r="O16" t="s">
+        <v>236</v>
+      </c>
+      <c r="P16" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>237</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>240</v>
+      </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1836,6 +2280,9 @@
       <c r="D17" t="b">
         <v>0</v>
       </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
@@ -1860,8 +2307,29 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="s">
+        <v>228</v>
+      </c>
+      <c r="O17" t="s">
+        <v>229</v>
+      </c>
+      <c r="P17" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>230</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -1874,6 +2342,9 @@
       <c r="D18" t="b">
         <v>0</v>
       </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
@@ -1898,8 +2369,29 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="s">
+        <v>221</v>
+      </c>
+      <c r="O18" t="s">
+        <v>222</v>
+      </c>
+      <c r="P18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>223</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>226</v>
+      </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1939,8 +2431,32 @@
       <c r="M19" t="b">
         <v>0</v>
       </c>
+      <c r="N19" t="s">
+        <v>213</v>
+      </c>
+      <c r="O19" t="s">
+        <v>214</v>
+      </c>
+      <c r="P19" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>215</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>219</v>
+      </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -1980,8 +2496,29 @@
       <c r="M20" t="b">
         <v>0</v>
       </c>
+      <c r="N20" t="s">
+        <v>206</v>
+      </c>
+      <c r="O20" t="s">
+        <v>207</v>
+      </c>
+      <c r="P20" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>208</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -1994,6 +2531,9 @@
       <c r="D21" t="b">
         <v>0</v>
       </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
@@ -2018,8 +2558,29 @@
       <c r="M21" t="b">
         <v>0</v>
       </c>
+      <c r="N21" t="s">
+        <v>199</v>
+      </c>
+      <c r="O21" t="s">
+        <v>200</v>
+      </c>
+      <c r="P21" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>201</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>204</v>
+      </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -2059,8 +2620,29 @@
       <c r="M22" t="b">
         <v>0</v>
       </c>
+      <c r="N22" t="s">
+        <v>192</v>
+      </c>
+      <c r="O22" t="s">
+        <v>193</v>
+      </c>
+      <c r="P22" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>195</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -2100,8 +2682,29 @@
       <c r="M23" t="b">
         <v>0</v>
       </c>
+      <c r="N23" t="s">
+        <v>185</v>
+      </c>
+      <c r="O23" t="s">
+        <v>186</v>
+      </c>
+      <c r="P23" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>187</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -2114,6 +2717,9 @@
       <c r="D24" t="b">
         <v>0</v>
       </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
@@ -2138,8 +2744,29 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="s">
+        <v>178</v>
+      </c>
+      <c r="O24" t="s">
+        <v>179</v>
+      </c>
+      <c r="P24" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>182</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>184</v>
+      </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -2179,8 +2806,32 @@
       <c r="M25" t="b">
         <v>0</v>
       </c>
+      <c r="N25" t="s">
+        <v>170</v>
+      </c>
+      <c r="O25" t="s">
+        <v>171</v>
+      </c>
+      <c r="P25" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>173</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>177</v>
+      </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -2193,6 +2844,9 @@
       <c r="D26" t="b">
         <v>0</v>
       </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
@@ -2217,8 +2871,29 @@
       <c r="M26" t="b">
         <v>0</v>
       </c>
+      <c r="N26" t="s">
+        <v>163</v>
+      </c>
+      <c r="O26" t="s">
+        <v>164</v>
+      </c>
+      <c r="P26" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>166</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>169</v>
+      </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -2258,10 +2933,91 @@
       <c r="M27" t="b">
         <v>0</v>
       </c>
+      <c r="N27" t="s">
+        <v>156</v>
+      </c>
+      <c r="O27" t="s">
+        <v>266</v>
+      </c>
+      <c r="P27" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>158</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>71</v>
+      </c>
+      <c r="B28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>264</v>
+      </c>
+      <c r="O28" t="s">
+        <v>267</v>
+      </c>
+      <c r="P28" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>269</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -2278,7 +3034,7 @@
     <hyperlink ref="U3" r:id="rId10" xr:uid="{3A2D2A5B-FEDE-43BF-A63F-C5BD502A0B2C}"/>
     <hyperlink ref="R4" r:id="rId11" xr:uid="{5BB4BDB8-B31F-4BA2-99CE-FF0A1E244A82}"/>
     <hyperlink ref="S4" r:id="rId12" xr:uid="{A84EA7BB-5B25-4C9A-A64B-E2ADDB90AA2F}"/>
-    <hyperlink ref="U4" r:id="rId13" xr:uid="{99DD846D-A35C-4453-A7AC-A9C59C3B9429}"/>
+    <hyperlink ref="T4" r:id="rId13" xr:uid="{99DD846D-A35C-4453-A7AC-A9C59C3B9429}"/>
     <hyperlink ref="R5" r:id="rId14" xr:uid="{5A548CF2-AF45-4CEC-A721-FA47E635B777}"/>
     <hyperlink ref="S5" r:id="rId15" xr:uid="{820428CB-BAD6-4736-B6E5-AE0A15F998D5}"/>
     <hyperlink ref="T5" r:id="rId16" xr:uid="{8ABBC501-3598-4079-916B-57AE1A01B315}"/>
@@ -2304,6 +3060,58 @@
     <hyperlink ref="S11" r:id="rId36" xr:uid="{D0273DE0-FDF7-4259-9359-895A6D75FF9B}"/>
     <hyperlink ref="T11" r:id="rId37" xr:uid="{631C9A88-45CD-4435-AFED-B262AA65C65F}"/>
     <hyperlink ref="U11" r:id="rId38" xr:uid="{9E72F33D-6C32-4DBE-AD0D-32AB72C38748}"/>
+    <hyperlink ref="R27" r:id="rId39" xr:uid="{F4D88E1F-FD18-401A-8448-E581D08827A0}"/>
+    <hyperlink ref="S27" r:id="rId40" xr:uid="{162C2B06-B6EF-4329-91F0-548F5BD9EFA0}"/>
+    <hyperlink ref="T27" r:id="rId41" xr:uid="{750C3678-4360-4A22-A39F-CACA9EAE293A}"/>
+    <hyperlink ref="U27" r:id="rId42" xr:uid="{3EA3F55A-7EE8-4436-91C1-5FF7B2887FBE}"/>
+    <hyperlink ref="R26" r:id="rId43" xr:uid="{F4C5D8E0-CB7C-4615-99E3-21B84CBCBC19}"/>
+    <hyperlink ref="S26" r:id="rId44" xr:uid="{8C64056A-94E8-4BBA-B4F6-B5BE3F5FCAFD}"/>
+    <hyperlink ref="T26" r:id="rId45" xr:uid="{42DDD62B-7428-46D6-BB72-A7FF9C17D302}"/>
+    <hyperlink ref="R25" r:id="rId46" xr:uid="{6A2D0557-6B9F-4FF6-8E43-C00044F50BCA}"/>
+    <hyperlink ref="S25" r:id="rId47" xr:uid="{BCCB9CF4-AE55-4DA2-BCB2-C111A6C35A09}"/>
+    <hyperlink ref="T25" r:id="rId48" xr:uid="{55C1FF24-EA95-4D86-89EC-1D21B128A101}"/>
+    <hyperlink ref="U25" r:id="rId49" xr:uid="{55790AB2-365E-46AA-BB69-B6ABACAECFD7}"/>
+    <hyperlink ref="R24" r:id="rId50" xr:uid="{E5394FA1-2EF8-458C-9427-6A13E03D2859}"/>
+    <hyperlink ref="S24" r:id="rId51" xr:uid="{1DA47B4F-6B10-47B7-9712-C6CA95BE1918}"/>
+    <hyperlink ref="T24" r:id="rId52" xr:uid="{7D844FC2-EE02-474F-AD82-240354A9BBC4}"/>
+    <hyperlink ref="S23" r:id="rId53" xr:uid="{5E6B28C9-4473-4E14-87E5-46F0A667EE40}"/>
+    <hyperlink ref="R23" r:id="rId54" xr:uid="{F11B9337-8F98-4605-A232-EB140A2D0932}"/>
+    <hyperlink ref="T23" r:id="rId55" xr:uid="{D0AAE5EE-E224-446C-8473-3E79A3577E64}"/>
+    <hyperlink ref="R22" r:id="rId56" xr:uid="{A26AB1CD-B21B-4FFF-B5A4-52243CDF8D39}"/>
+    <hyperlink ref="S22" r:id="rId57" xr:uid="{9C305003-AB95-4B21-9560-7EF84BF4AFE4}"/>
+    <hyperlink ref="T22" r:id="rId58" xr:uid="{C5F6A4BE-1C37-49B9-8DE3-75AFD6B5CA03}"/>
+    <hyperlink ref="R21" r:id="rId59" xr:uid="{41F2E7AC-9C5F-4931-9E7D-30D69105EDCE}"/>
+    <hyperlink ref="S21" r:id="rId60" xr:uid="{90D7A610-674B-413B-8EA8-FA650AD2D5F6}"/>
+    <hyperlink ref="T21" r:id="rId61" xr:uid="{15F153F3-4ADA-4F38-A6F9-641435C0FA6C}"/>
+    <hyperlink ref="R20" r:id="rId62" xr:uid="{A6791A94-0CEA-46D6-9C70-25544BAA3279}"/>
+    <hyperlink ref="S20" r:id="rId63" xr:uid="{EAA46671-D8EB-439E-9304-C9D25CC4379F}"/>
+    <hyperlink ref="T20" r:id="rId64" xr:uid="{2DF465F8-B3FF-4844-B595-BC5B6339F330}"/>
+    <hyperlink ref="R19" r:id="rId65" xr:uid="{E9B4F605-4949-43B7-8C91-748EA7ACEA55}"/>
+    <hyperlink ref="S19" r:id="rId66" xr:uid="{2EB71799-A44C-4AED-9993-13C2E49354F0}"/>
+    <hyperlink ref="T19" r:id="rId67" xr:uid="{E02528F0-D012-4837-B25D-0BCBD61F1A1A}"/>
+    <hyperlink ref="U19" r:id="rId68" xr:uid="{52C26AD7-502E-4A89-8D5F-C680C5131005}"/>
+    <hyperlink ref="R18" r:id="rId69" xr:uid="{51560079-CE52-45F4-8612-0C3D135FFBAA}"/>
+    <hyperlink ref="S18" r:id="rId70" xr:uid="{96CF00E4-B5D4-4A98-99F5-B7450E7FB0BC}"/>
+    <hyperlink ref="T18" r:id="rId71" xr:uid="{78DFBCF7-6885-4A7A-9DCE-71879C2665B9}"/>
+    <hyperlink ref="R17" r:id="rId72" xr:uid="{E4B10D4C-2209-47CA-953E-9F7CA31D2A62}"/>
+    <hyperlink ref="S17" r:id="rId73" xr:uid="{5E274855-DC51-4F2E-857D-BA5CE2ADC468}"/>
+    <hyperlink ref="T17" r:id="rId74" xr:uid="{815A703A-0100-4D64-961C-CD6C5E9FECA7}"/>
+    <hyperlink ref="R16" r:id="rId75" xr:uid="{B606C602-7968-4392-91E0-BFCD582B406D}"/>
+    <hyperlink ref="S16" r:id="rId76" xr:uid="{342E48DA-2DD2-41D5-A324-DE2E3839D31F}"/>
+    <hyperlink ref="T16" r:id="rId77" xr:uid="{60D63124-E641-4FED-86D7-5B247833EF57}"/>
+    <hyperlink ref="R15" r:id="rId78" xr:uid="{BB8734EC-A2DC-4903-9340-B4456D3F531E}"/>
+    <hyperlink ref="S15" r:id="rId79" xr:uid="{0EA7030C-1995-4E4C-9991-6DEAF7D76B81}"/>
+    <hyperlink ref="T15" r:id="rId80" xr:uid="{B2E6BA52-8BF2-4671-A093-46C289293215}"/>
+    <hyperlink ref="R14" r:id="rId81" xr:uid="{07ED557F-F7B9-4643-89E4-E1A89F87B41C}"/>
+    <hyperlink ref="S14" r:id="rId82" xr:uid="{BD64EDED-2574-4A71-8E6E-87677651F97F}"/>
+    <hyperlink ref="T14" r:id="rId83" xr:uid="{013874C3-8EDE-47FE-BFF5-89410CE79DD1}"/>
+    <hyperlink ref="R13" r:id="rId84" xr:uid="{5C49FC0F-A73D-4261-9378-00F6DB87D2EE}"/>
+    <hyperlink ref="S13" r:id="rId85" xr:uid="{E94D15F5-754A-4959-959E-E19ED76B572B}"/>
+    <hyperlink ref="T13" r:id="rId86" xr:uid="{886EA406-113B-4DD8-86F5-AA232309C73E}"/>
+    <hyperlink ref="U13" r:id="rId87" xr:uid="{6B872088-EB7E-415E-A5BB-D1890108B21F}"/>
+    <hyperlink ref="R28" r:id="rId88" xr:uid="{286EF75F-C3C9-47CD-8D80-8DDC48CC0D9E}"/>
+    <hyperlink ref="S28" r:id="rId89" xr:uid="{9CA08672-A9F4-4264-A5E7-D89F00291D70}"/>
+    <hyperlink ref="T28" r:id="rId90" xr:uid="{C358C149-3299-4AAA-A7E7-2EFD38D495A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/publications/data.xlsx
+++ b/publications/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91720c579d88d817/Documents/GitHub/rjjanse.github.io/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="329" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F2ECCDA-1BA4-432F-BE4D-3CB2B0E689C4}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF3B843-3386-4722-BAC7-F958B0960E37}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
   <si>
     <t>id</t>
   </si>
@@ -65,9 +65,6 @@
     <t>pfd_cvd</t>
   </si>
   <si>
-    <t>pvd_neph</t>
-  </si>
-  <si>
     <t>pfd_dm</t>
   </si>
   <si>
@@ -855,6 +852,12 @@
   </si>
   <si>
     <t>https://europepmc.org/article/MED/41577248</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>pfd_neph</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C16EB68-4490-458C-8DAB-883C12CD690B}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
@@ -1254,7 +1257,7 @@
     <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1265,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1286,45 +1289,48 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
+        <v>273</v>
+      </c>
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
-        <v>19</v>
+      <c r="V1" t="s">
+        <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
         <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -1360,98 +1366,104 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" t="s">
         <v>80</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>81</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O3" t="s">
         <v>86</v>
       </c>
+      <c r="P3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>89</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" t="s">
-        <v>87</v>
-      </c>
-      <c r="P3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>90</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -1487,163 +1499,172 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" t="s">
         <v>95</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>96</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>97</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
         <v>101</v>
       </c>
+      <c r="O5" t="s">
+        <v>102</v>
+      </c>
+      <c r="P5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>107</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>102</v>
-      </c>
-      <c r="O5" t="s">
-        <v>103</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
         <v>104</v>
       </c>
-      <c r="Q5" t="s">
-        <v>108</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="U5" s="1" t="s">
+      <c r="O6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P6" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q6" t="s">
         <v>112</v>
       </c>
+      <c r="R6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>105</v>
-      </c>
-      <c r="O6" t="s">
-        <v>106</v>
-      </c>
-      <c r="P6" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>113</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
@@ -1679,33 +1700,36 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
+        <v>117</v>
+      </c>
+      <c r="O7" t="s">
         <v>118</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>119</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>120</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="T7" s="1" t="s">
-        <v>124</v>
+      <c r="V7" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
         <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -1741,33 +1765,36 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8" t="s">
         <v>125</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>126</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>127</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>131</v>
+      <c r="V8" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
@@ -1803,36 +1830,39 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O9" t="s">
         <v>132</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>133</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>134</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>139</v>
+      <c r="V9" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
         <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
@@ -1868,33 +1898,36 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
+        <v>139</v>
+      </c>
+      <c r="O10" t="s">
         <v>140</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>141</v>
       </c>
-      <c r="P10" t="s">
-        <v>142</v>
-      </c>
       <c r="Q10" t="s">
+        <v>146</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="T10" s="1" t="s">
-        <v>150</v>
+      <c r="V10" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -1930,98 +1963,104 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
+        <v>142</v>
+      </c>
+      <c r="O11" t="s">
         <v>143</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>144</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>145</v>
       </c>
-      <c r="Q11" t="s">
-        <v>146</v>
-      </c>
       <c r="R11" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="U11" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>154</v>
+      <c r="V11" t="b">
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
         <v>21</v>
       </c>
-      <c r="C12" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>22</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>23</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T12" s="1" t="s">
-        <v>28</v>
+      <c r="V12" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
         <v>49</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
@@ -2057,36 +2096,39 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
+        <v>255</v>
+      </c>
+      <c r="O13" t="s">
         <v>256</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q13" t="s">
         <v>257</v>
       </c>
-      <c r="P13" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="R13" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="T13" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="T13" s="1" t="s">
+      <c r="U13" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>262</v>
+      <c r="V13" t="b">
+        <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
         <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -2122,33 +2164,36 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
+        <v>248</v>
+      </c>
+      <c r="O14" t="s">
         <v>249</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q14" t="s">
         <v>250</v>
       </c>
-      <c r="P14" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="R14" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>254</v>
+      <c r="V14" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -2184,33 +2229,36 @@
         <v>1</v>
       </c>
       <c r="N15" t="s">
+        <v>241</v>
+      </c>
+      <c r="O15" t="s">
         <v>242</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q15" t="s">
         <v>243</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="Q15" t="s">
-        <v>244</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>248</v>
+      <c r="V15" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
         <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
@@ -2246,33 +2294,36 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
+        <v>234</v>
+      </c>
+      <c r="O16" t="s">
         <v>235</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q16" t="s">
         <v>236</v>
       </c>
-      <c r="P16" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="R16" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="T16" s="1" t="s">
-        <v>240</v>
+      <c r="V16" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
         <v>57</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
@@ -2308,33 +2359,36 @@
         <v>1</v>
       </c>
       <c r="N17" t="s">
+        <v>227</v>
+      </c>
+      <c r="O17" t="s">
         <v>228</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q17" t="s">
         <v>229</v>
       </c>
-      <c r="P17" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q17" t="s">
+      <c r="R17" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="T17" s="1" t="s">
-        <v>233</v>
+      <c r="V17" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
         <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
@@ -2370,160 +2424,169 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
+        <v>220</v>
+      </c>
+      <c r="O18" t="s">
         <v>221</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q18" t="s">
         <v>222</v>
       </c>
-      <c r="P18" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q18" t="s">
+      <c r="R18" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="T18" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>226</v>
+      <c r="V18" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
         <v>61</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>212</v>
+      </c>
+      <c r="O19" t="s">
+        <v>213</v>
+      </c>
+      <c r="P19" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>214</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>62</v>
       </c>
-      <c r="C19" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>213</v>
-      </c>
-      <c r="O19" t="s">
-        <v>214</v>
-      </c>
-      <c r="P19" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>215</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>219</v>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>205</v>
+      </c>
+      <c r="O20" t="s">
+        <v>206</v>
+      </c>
+      <c r="P20" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>207</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>206</v>
-      </c>
-      <c r="O20" t="s">
-        <v>207</v>
-      </c>
-      <c r="P20" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>208</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
@@ -2559,95 +2622,101 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
+        <v>198</v>
+      </c>
+      <c r="O21" t="s">
         <v>199</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q21" t="s">
         <v>200</v>
       </c>
-      <c r="P21" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q21" t="s">
+      <c r="R21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="T21" s="1" t="s">
-        <v>204</v>
+      <c r="V21" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>191</v>
+      </c>
+      <c r="O22" t="s">
+        <v>192</v>
+      </c>
+      <c r="P22" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>194</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>65</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>73</v>
-      </c>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>192</v>
-      </c>
-      <c r="O22" t="s">
-        <v>193</v>
-      </c>
-      <c r="P22" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>195</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
@@ -2683,33 +2752,36 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
+        <v>184</v>
+      </c>
+      <c r="O23" t="s">
         <v>185</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q23" t="s">
         <v>186</v>
       </c>
-      <c r="P23" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q23" t="s">
+      <c r="R23" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="S23" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="T23" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>190</v>
+      <c r="V23" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" t="b">
         <v>0</v>
@@ -2745,98 +2817,104 @@
         <v>1</v>
       </c>
       <c r="N24" t="s">
+        <v>177</v>
+      </c>
+      <c r="O24" t="s">
         <v>178</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>179</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
+        <v>181</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="S24" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="S24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="T24" s="1" t="s">
-        <v>184</v>
+      <c r="V24" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>169</v>
+      </c>
+      <c r="O25" t="s">
+        <v>170</v>
+      </c>
+      <c r="P25" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>172</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>68</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>76</v>
-      </c>
-      <c r="C25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>170</v>
-      </c>
-      <c r="O25" t="s">
-        <v>171</v>
-      </c>
-      <c r="P25" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>173</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
       </c>
       <c r="C26" t="b">
         <v>0</v>
@@ -2872,98 +2950,104 @@
         <v>0</v>
       </c>
       <c r="N26" t="s">
+        <v>162</v>
+      </c>
+      <c r="O26" t="s">
         <v>163</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>164</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>165</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="R26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="S26" s="1" t="s">
+      <c r="T26" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="T26" s="1" t="s">
-        <v>169</v>
+      <c r="V26" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" t="s">
+        <v>265</v>
+      </c>
+      <c r="P27" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>157</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>70</v>
       </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="b">
-        <v>0</v>
-      </c>
-      <c r="M27" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>156</v>
-      </c>
-      <c r="O27" t="s">
-        <v>266</v>
-      </c>
-      <c r="P27" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>158</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
       <c r="B28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
@@ -2999,25 +3083,28 @@
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O28" t="s">
+        <v>266</v>
+      </c>
+      <c r="P28" t="s">
         <v>267</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>268</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="S28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="T28" s="1" t="s">
-        <v>272</v>
+      <c r="V28" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/publications/data.xlsx
+++ b/publications/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91720c579d88d817/Documents/GitHub/rjjanse.github.io/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="336" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF3B843-3386-4722-BAC7-F958B0960E37}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2777A451-A596-4671-A46C-1E006DF020BE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
   </bookViews>
@@ -263,9 +263,6 @@
     <t>Retrieval practice using VSAQs vs. MCQs</t>
   </si>
   <si>
-    <t>On machine learning for prediction modellign</t>
-  </si>
-  <si>
     <t>Cardiometabolic proteins and kidney function</t>
   </si>
   <si>
@@ -858,6 +855,9 @@
   </si>
   <si>
     <t>pfd_neph</t>
+  </si>
+  <si>
+    <t>On machine learning for prediction modelling</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1289,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
@@ -1322,7 +1322,7 @@
         <v>18</v>
       </c>
       <c r="V1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
@@ -1366,25 +1366,25 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" t="s">
         <v>79</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>80</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>81</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="V2" t="b">
         <v>0</v>
@@ -1431,28 +1431,28 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" t="s">
         <v>87</v>
       </c>
-      <c r="O3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>88</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1499,25 +1499,25 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O4" t="s">
         <v>94</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>95</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>96</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
@@ -1564,28 +1564,28 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" t="s">
         <v>101</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>102</v>
       </c>
-      <c r="P5" t="s">
-        <v>103</v>
-      </c>
       <c r="Q5" t="s">
+        <v>106</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1632,28 +1632,28 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" t="s">
         <v>104</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>105</v>
       </c>
-      <c r="P6" t="s">
-        <v>106</v>
-      </c>
       <c r="Q6" t="s">
+        <v>111</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1700,25 +1700,25 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" t="s">
         <v>117</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>118</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>119</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
+        <v>123</v>
+      </c>
+      <c r="O8" t="s">
         <v>124</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>125</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>126</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1830,28 +1830,28 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
+        <v>130</v>
+      </c>
+      <c r="O9" t="s">
         <v>131</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>132</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>133</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -1898,25 +1898,25 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
+        <v>138</v>
+      </c>
+      <c r="O10" t="s">
         <v>139</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>140</v>
       </c>
-      <c r="P10" t="s">
-        <v>141</v>
-      </c>
       <c r="Q10" t="s">
+        <v>145</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -1963,28 +1963,28 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" t="s">
         <v>142</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>143</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>144</v>
       </c>
-      <c r="Q11" t="s">
-        <v>145</v>
-      </c>
       <c r="R11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="U11" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2096,28 +2096,28 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
+        <v>254</v>
+      </c>
+      <c r="O13" t="s">
         <v>255</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q13" t="s">
         <v>256</v>
       </c>
-      <c r="P13" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="R13" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="T13" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="T13" s="1" t="s">
+      <c r="U13" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
@@ -2164,25 +2164,25 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
+        <v>247</v>
+      </c>
+      <c r="O14" t="s">
         <v>248</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q14" t="s">
         <v>249</v>
       </c>
-      <c r="P14" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="R14" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="V14" t="b">
         <v>0</v>
@@ -2229,25 +2229,25 @@
         <v>1</v>
       </c>
       <c r="N15" t="s">
+        <v>240</v>
+      </c>
+      <c r="O15" t="s">
         <v>241</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q15" t="s">
         <v>242</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>243</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
@@ -2294,25 +2294,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
+        <v>233</v>
+      </c>
+      <c r="O16" t="s">
         <v>234</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q16" t="s">
         <v>235</v>
       </c>
-      <c r="P16" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="R16" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="V16" t="b">
         <v>0</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="N17" t="s">
+        <v>226</v>
+      </c>
+      <c r="O17" t="s">
         <v>227</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q17" t="s">
         <v>228</v>
       </c>
-      <c r="P17" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q17" t="s">
+      <c r="R17" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="V17" t="b">
         <v>0</v>
@@ -2424,25 +2424,25 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
+        <v>219</v>
+      </c>
+      <c r="O18" t="s">
         <v>220</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q18" t="s">
         <v>221</v>
       </c>
-      <c r="P18" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q18" t="s">
+      <c r="R18" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="T18" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="V18" t="b">
         <v>0</v>
@@ -2489,28 +2489,28 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
+        <v>211</v>
+      </c>
+      <c r="O19" t="s">
         <v>212</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q19" t="s">
         <v>213</v>
       </c>
-      <c r="P19" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q19" t="s">
+      <c r="R19" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="S19" s="1" t="s">
+      <c r="T19" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="T19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="V19" t="b">
         <v>0</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
+        <v>204</v>
+      </c>
+      <c r="O20" t="s">
         <v>205</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q20" t="s">
         <v>206</v>
       </c>
-      <c r="P20" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="R20" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="T20" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="V20" t="b">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
@@ -2622,25 +2622,25 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
+        <v>197</v>
+      </c>
+      <c r="O21" t="s">
         <v>198</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q21" t="s">
         <v>199</v>
       </c>
-      <c r="P21" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q21" t="s">
+      <c r="R21" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="V21" t="b">
         <v>0</v>
@@ -2687,25 +2687,25 @@
         <v>0</v>
       </c>
       <c r="N22" t="s">
+        <v>190</v>
+      </c>
+      <c r="O22" t="s">
         <v>191</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>192</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>193</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="V22" t="b">
         <v>0</v>
@@ -2752,25 +2752,25 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
+        <v>183</v>
+      </c>
+      <c r="O23" t="s">
         <v>184</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q23" t="s">
         <v>185</v>
       </c>
-      <c r="P23" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q23" t="s">
+      <c r="R23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="S23" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="T23" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="V23" t="b">
         <v>0</v>
@@ -2817,25 +2817,25 @@
         <v>1</v>
       </c>
       <c r="N24" t="s">
+        <v>176</v>
+      </c>
+      <c r="O24" t="s">
         <v>177</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>178</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
+        <v>180</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="S24" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="S24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="V24" t="b">
         <v>0</v>
@@ -2846,7 +2846,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
@@ -2882,28 +2882,28 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
+        <v>168</v>
+      </c>
+      <c r="O25" t="s">
         <v>169</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>170</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>171</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="R25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="S25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="U25" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="V25" t="b">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" t="b">
         <v>0</v>
@@ -2950,25 +2950,25 @@
         <v>0</v>
       </c>
       <c r="N26" t="s">
+        <v>161</v>
+      </c>
+      <c r="O26" t="s">
         <v>162</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>163</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>164</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="R26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="S26" s="1" t="s">
+      <c r="T26" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="V26" t="b">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C27" t="b">
         <v>1</v>
@@ -3015,28 +3015,28 @@
         <v>0</v>
       </c>
       <c r="N27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O27" t="s">
+        <v>264</v>
+      </c>
+      <c r="P27" t="s">
         <v>155</v>
       </c>
-      <c r="O27" t="s">
-        <v>265</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>156</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="S27" s="1" t="s">
+      <c r="T27" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="T27" s="1" t="s">
+      <c r="U27" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="V27" t="b">
         <v>0</v>
@@ -3047,7 +3047,7 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
@@ -3083,25 +3083,25 @@
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O28" t="s">
+        <v>265</v>
+      </c>
+      <c r="P28" t="s">
         <v>266</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>267</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="S28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="V28" t="b">
         <v>0</v>

--- a/publications/data.xlsx
+++ b/publications/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91720c579d88d817/Documents/GitHub/rjjanse.github.io/publications/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umcutrecht-my.sharepoint.com/personal/r_j_janse-5_umcutrecht_nl/Documents/Documenten/GitHub/rjjanse.github.io/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2777A451-A596-4671-A46C-1E006DF020BE}"/>
+  <xr:revisionPtr revIDLastSave="361" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD5F925C-AB5A-A644-9B4D-ED75C5B083F9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="282">
   <si>
     <t>id</t>
   </si>
@@ -593,9 +593,6 @@
     <t>Driehuis E, Janse RJ, Roeterdink AJ, Konijn WS, van Lieshout TS, Volgers TJFM, Goto NA, Broese van Groenou MI, Dekker FW, van Jaarsveld BC, Abrahams AC</t>
   </si>
   <si>
-    <t>Clinical Kidney Journal - 7 October 2024</t>
-  </si>
-  <si>
     <t>https://pubmed.ncbi.nlm.nih.gov/39493262/</t>
   </si>
   <si>
@@ -858,6 +855,33 @@
   </si>
   <si>
     <t>On machine learning for prediction modelling</t>
+  </si>
+  <si>
+    <t>janse-2026-ije</t>
+  </si>
+  <si>
+    <t>Epidemiology shouldn't be automated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why can’t epidemiology be automated (yet)? Perhaps it shouldn’t be </t>
+  </si>
+  <si>
+    <t>Janse RJ, Meulenbeld A</t>
+  </si>
+  <si>
+    <t>In a recent issue of the International Journal of Epidemiology, Bann and colleagues describe several ways in which artificial intelligence (AI), and especially generative AI (such as large language models), may help optimize epidemiological research, ranging from hypothesis generation to the dissemination of results. Although we agree that AI provides opportunities for reducing repetitive tasks and speeding up scientific work, we argue that it is undesirable to strive for the degree of epidemiological automation described by Bann et al.</t>
+  </si>
+  <si>
+    <t>International Journal of Epidemiology - 07 May 2026</t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 07 October 2024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ije/dyag065</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/42096300/</t>
   </si>
 </sst>
 </file>
@@ -923,10 +947,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1246,18 +1266,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C16EB68-4490-458C-8DAB-883C12CD690B}">
-  <dimension ref="A1:V28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" customWidth="1"/>
+    <col min="17" max="17" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
@@ -1322,10 +1342,10 @@
         <v>18</v>
       </c>
       <c r="V1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1390,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1458,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1523,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1591,7 +1611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1659,7 +1679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1724,7 +1744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1789,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1857,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1922,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -1990,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2055,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -2096,34 +2116,34 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
+        <v>253</v>
+      </c>
+      <c r="O13" t="s">
         <v>254</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q13" t="s">
         <v>255</v>
       </c>
-      <c r="P13" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="R13" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="T13" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="T13" s="1" t="s">
+      <c r="U13" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="V13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -2164,31 +2184,31 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
+        <v>246</v>
+      </c>
+      <c r="O14" t="s">
         <v>247</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q14" t="s">
         <v>248</v>
       </c>
-      <c r="P14" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="R14" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="V14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -2229,31 +2249,31 @@
         <v>1</v>
       </c>
       <c r="N15" t="s">
+        <v>239</v>
+      </c>
+      <c r="O15" t="s">
         <v>240</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q15" t="s">
         <v>241</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="Q15" t="s">
-        <v>242</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="V15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -2294,31 +2314,31 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
+        <v>232</v>
+      </c>
+      <c r="O16" t="s">
         <v>233</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q16" t="s">
         <v>234</v>
       </c>
-      <c r="P16" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="R16" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="T16" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="V16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -2359,31 +2379,31 @@
         <v>1</v>
       </c>
       <c r="N17" t="s">
+        <v>225</v>
+      </c>
+      <c r="O17" t="s">
         <v>226</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q17" t="s">
         <v>227</v>
       </c>
-      <c r="P17" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q17" t="s">
+      <c r="R17" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="T17" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="V17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -2424,31 +2444,31 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
+        <v>218</v>
+      </c>
+      <c r="O18" t="s">
         <v>219</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q18" t="s">
         <v>220</v>
       </c>
-      <c r="P18" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q18" t="s">
+      <c r="R18" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="T18" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="V18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -2489,34 +2509,34 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
+        <v>210</v>
+      </c>
+      <c r="O19" t="s">
         <v>211</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q19" t="s">
         <v>212</v>
       </c>
-      <c r="P19" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q19" t="s">
+      <c r="R19" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="S19" s="1" t="s">
+      <c r="T19" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="T19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="U19" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="V19" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -2557,31 +2577,31 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
+        <v>203</v>
+      </c>
+      <c r="O20" t="s">
         <v>204</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q20" t="s">
         <v>205</v>
       </c>
-      <c r="P20" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="R20" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="T20" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="T20" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="V20" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -2622,31 +2642,31 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
+        <v>196</v>
+      </c>
+      <c r="O21" t="s">
         <v>197</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q21" t="s">
         <v>198</v>
       </c>
-      <c r="P21" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q21" t="s">
+      <c r="R21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="T21" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="V21" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -2687,31 +2707,31 @@
         <v>0</v>
       </c>
       <c r="N22" t="s">
+        <v>189</v>
+      </c>
+      <c r="O22" t="s">
         <v>190</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>191</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>192</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="T22" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="V22" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -2758,25 +2778,25 @@
         <v>184</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q23" t="s">
+        <v>279</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="S23" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="T23" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="V23" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -2841,12 +2861,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
@@ -2909,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -2974,7 +2994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -3018,7 +3038,7 @@
         <v>154</v>
       </c>
       <c r="O27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P27" t="s">
         <v>155</v>
@@ -3042,12 +3062,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
@@ -3083,27 +3103,89 @@
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O28" t="s">
+        <v>264</v>
+      </c>
+      <c r="P28" t="s">
         <v>265</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>266</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="S28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="T28" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="V28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>273</v>
+      </c>
+      <c r="B29" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>275</v>
+      </c>
+      <c r="O29" t="s">
+        <v>276</v>
+      </c>
+      <c r="P29" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>278</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="V29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3199,6 +3281,8 @@
     <hyperlink ref="R28" r:id="rId88" xr:uid="{286EF75F-C3C9-47CD-8D80-8DDC48CC0D9E}"/>
     <hyperlink ref="S28" r:id="rId89" xr:uid="{9CA08672-A9F4-4264-A5E7-D89F00291D70}"/>
     <hyperlink ref="T28" r:id="rId90" xr:uid="{C358C149-3299-4AAA-A7E7-2EFD38D495A7}"/>
+    <hyperlink ref="R29" r:id="rId91" xr:uid="{EC911316-F509-CE4A-BCE5-29539E2664E2}"/>
+    <hyperlink ref="S29" r:id="rId92" xr:uid="{9A96AF52-38F7-144F-9950-A702802D8F16}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/publications/data.xlsx
+++ b/publications/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umcutrecht-my.sharepoint.com/personal/r_j_janse-5_umcutrecht_nl/Documents/Documenten/GitHub/rjjanse.github.io/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="361" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD5F925C-AB5A-A644-9B4D-ED75C5B083F9}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD6600C5-4D70-E548-8CE9-1354D7CAD916}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
   <si>
     <t>id</t>
   </si>
@@ -882,6 +882,27 @@
   </si>
   <si>
     <t>https://pubmed.ncbi.nlm.nih.gov/42096300/</t>
+  </si>
+  <si>
+    <t>veltkamp-2026-ckj</t>
+  </si>
+  <si>
+    <t>Long-term risks of major adverse cardiovascular events after acute kidney injury: A systematic review and meta-analysis</t>
+  </si>
+  <si>
+    <t>Long-term risks of MACE after AKI</t>
+  </si>
+  <si>
+    <t>Veltkamp DMJ, Zwank F, Tiel Groenestege WM, Verhaar MC, Van Solinge WW, Haitjema S, Vernooij RWM, Janse RJ</t>
+  </si>
+  <si>
+    <t>Background and Aims: Acute kidney injury (AKI) is increasingly recognized as a long-term risk factor for chronic kidney disease and cardiovascular disease (CVD). However, it remains uncertain which patients with AKI are at greatest CVD risk. We performed a systematic review and meta-analysis to quantify CVD risks post-AKI and to determine whether these risks differ by AKI severity, duration, and clinical setting. Methods: PubMed and Embase were systematically searched for studies comparing individuals with and without AKI and reporting major adverse cardiovascular events (MACE) or individual outcomes such as myocardial infarction (MI), stroke, heart failure (HF), or cardiovascular mortality. Follow-up was at least one year. Relative risks (RRs) were pooled in meta-analyses using random-effects models. Subgroup and meta-regression analyses were used to explore heterogeneity across patient and AKI characteristics, and clinical settings. Results: We included 54 studies comprising 1 261 090 individuals, of whom 290 648 experienced AKI. Meta-analyses showed that AKI was associated with a RR of 1.97 [95%CI 1.67–2.27] for MACE (13.9% overall incidence), 1.64 [95%CI 1.38–1.89] for MI (3.5% overall incidence), 1.36 [95%CI 1.13–1.59] for stroke (1.7% overall incidence), 1.92 [95%CI 1.67–2.16] for HF (3.5% overall incidence), and 1.86 [95%CI 1.59–2.13] for cardiovascular mortality (9.4% overall incidence), compared to patients without AKI. Elevated risks were observed across all AKI stages and durations and in patients across all studied clinical settings, including non-cardiac care. The highest RRs were shown for more severe AKI stages and longer AKI durations. Older age and lower baseline estimated glomerular filtration rate were associated with even higher risk of MACE compared to patients without AKI. Conclusions: AKI is followed by an increase in CVD risk, even after AKI with low severity. These findings highlight AKI as a clinically relevant CVD risk marker and support the need for targeted post-AKI care management to prevent future cardiovascular events.</t>
+  </si>
+  <si>
+    <t>Clinical Kidney Journal - 07 May 2026</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/ckj/sfag145</t>
   </si>
 </sst>
 </file>
@@ -926,11 +947,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1266,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C16EB68-4490-458C-8DAB-883C12CD690B}">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
@@ -3188,6 +3210,68 @@
       <c r="V29" t="b">
         <v>0</v>
       </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B30" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>283</v>
+      </c>
+      <c r="O30" t="s">
+        <v>285</v>
+      </c>
+      <c r="P30" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>287</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="M32" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3283,6 +3367,7 @@
     <hyperlink ref="T28" r:id="rId90" xr:uid="{C358C149-3299-4AAA-A7E7-2EFD38D495A7}"/>
     <hyperlink ref="R29" r:id="rId91" xr:uid="{EC911316-F509-CE4A-BCE5-29539E2664E2}"/>
     <hyperlink ref="S29" r:id="rId92" xr:uid="{9A96AF52-38F7-144F-9950-A702802D8F16}"/>
+    <hyperlink ref="R30" r:id="rId93" xr:uid="{802EB42C-A9FD-3D43-995D-7C388D7E67EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/publications/data.xlsx
+++ b/publications/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umcutrecht-my.sharepoint.com/personal/r_j_janse-5_umcutrecht_nl/Documents/Documenten/GitHub/rjjanse.github.io/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD6600C5-4D70-E548-8CE9-1354D7CAD916}"/>
+  <xr:revisionPtr revIDLastSave="389" documentId="8_{73F58B86-8A8C-44D2-97E6-524D5F699074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D07A1881-EC02-4849-960E-2C38EC1090E5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{0D0B8934-B9C8-41E7-88BE-115311452A91}"/>
   </bookViews>
@@ -947,12 +947,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1288,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C16EB68-4490-458C-8DAB-883C12CD690B}">
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
@@ -3225,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -3269,9 +3268,6 @@
       <c r="V30" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="M32" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
